--- a/data/trans_orig/IP08-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP08-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>6895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17918</t>
+          <t>17031</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23826</t>
+          <t>23936</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>42515</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49466</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42299</t>
+          <t>43186</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52999</t>
+          <t>53322</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88959</t>
+          <t>88849</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101450</t>
+          <t>100938</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17179</t>
+          <t>17959</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>15602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30377</t>
+          <t>29856</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86128</t>
+          <t>85525</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95587</t>
+          <t>95709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91578</t>
+          <t>90798</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101547</t>
+          <t>101537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179942</t>
+          <t>180463</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194960</t>
+          <t>194717</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15241</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57728</t>
+          <t>57767</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65564</t>
+          <t>65273</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60904</t>
+          <t>60863</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68434</t>
+          <t>67843</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122683</t>
+          <t>121356</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132665</t>
+          <t>131883</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20338</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63587</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71541</t>
+          <t>71366</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66673</t>
+          <t>66016</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75177</t>
+          <t>75079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133634</t>
+          <t>133039</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144814</t>
+          <t>145246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>10016</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>15889</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>31836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39469</t>
+          <t>39695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>35781</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42765</t>
+          <t>42752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70455</t>
+          <t>70806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80579</t>
+          <t>80982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11664</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50530</t>
+          <t>50526</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55385</t>
+          <t>55391</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49711</t>
+          <t>50194</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57238</t>
+          <t>57281</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104123</t>
+          <t>104085</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111822</t>
+          <t>112072</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22263</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18026</t>
+          <t>18122</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33748</t>
+          <t>33372</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112492</t>
+          <t>112914</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123014</t>
+          <t>123140</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>113392</t>
+          <t>113863</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>125579</t>
+          <t>126153</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>230529</t>
+          <t>230905</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>246251</t>
+          <t>246155</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17560</t>
+          <t>17930</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>16362</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29925</t>
+          <t>30537</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>25949</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43920</t>
+          <t>43625</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>140344</t>
+          <t>139974</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>151149</t>
+          <t>150695</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>133438</t>
+          <t>132826</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>147829</t>
+          <t>147001</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>277347</t>
+          <t>277642</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>295012</t>
+          <t>295318</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>44360</t>
+          <t>45465</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>69145</t>
+          <t>68573</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>69713</t>
+          <t>69555</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>97968</t>
+          <t>98523</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>123077</t>
+          <t>120983</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>160145</t>
+          <t>159801</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>611876</t>
+          <t>612448</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>636661</t>
+          <t>635556</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>624037</t>
+          <t>623482</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>652292</t>
+          <t>652450</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1242881</t>
+          <t>1243225</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1279949</t>
+          <t>1282043</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20324</t>
+          <t>21409</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25145</t>
+          <t>25476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24645</t>
+          <t>24338</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41149</t>
+          <t>41480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37103</t>
+          <t>36018</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47619</t>
+          <t>47202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39664</t>
+          <t>39333</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52629</t>
+          <t>52555</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81087</t>
+          <t>80756</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97591</t>
+          <t>97898</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,09%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17804</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32590</t>
+          <t>31613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86317</t>
+          <t>86511</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97004</t>
+          <t>97223</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93355</t>
+          <t>93382</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103583</t>
+          <t>103874</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183282</t>
+          <t>184259</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>198538</t>
+          <t>198952</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15119</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10989</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22210</t>
+          <t>22437</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53059</t>
+          <t>53292</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62697</t>
+          <t>62897</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60265</t>
+          <t>60294</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67916</t>
+          <t>68455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>117222</t>
+          <t>116995</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129579</t>
+          <t>129659</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18883</t>
+          <t>18864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69081</t>
+          <t>68954</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76192</t>
+          <t>75921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68695</t>
+          <t>68241</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78450</t>
+          <t>78473</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>141112</t>
+          <t>141131</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153554</t>
+          <t>152803</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9695</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20761</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34023</t>
+          <t>33976</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41633</t>
+          <t>41606</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32943</t>
+          <t>32466</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41603</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69892</t>
+          <t>68650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80958</t>
+          <t>80540</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14838</t>
+          <t>14295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9765</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21646</t>
+          <t>22672</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45171</t>
+          <t>45685</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53145</t>
+          <t>53085</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45407</t>
+          <t>45950</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54971</t>
+          <t>54961</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94584</t>
+          <t>93558</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>106465</t>
+          <t>106248</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,41%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18934</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12320</t>
+          <t>11967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>24897</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23061</t>
+          <t>22499</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39997</t>
+          <t>39717</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119784</t>
+          <t>119074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>130557</t>
+          <t>130558</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>120577</t>
+          <t>120842</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>133419</t>
+          <t>133772</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>244460</t>
+          <t>244740</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>261396</t>
+          <t>261958</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12546</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26029</t>
+          <t>25948</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16144</t>
+          <t>16019</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31055</t>
+          <t>30093</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31585</t>
+          <t>32696</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52669</t>
+          <t>51896</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137945</t>
+          <t>138026</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>151428</t>
+          <t>151495</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140260</t>
+          <t>141222</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155171</t>
+          <t>155296</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>282620</t>
+          <t>283393</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>303704</t>
+          <t>302593</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>70716</t>
+          <t>69593</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>97881</t>
+          <t>97242</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>87689</t>
+          <t>87486</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>118812</t>
+          <t>116351</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>164766</t>
+          <t>164447</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>207436</t>
+          <t>205744</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>612776</t>
+          <t>613415</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>639941</t>
+          <t>641064</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>634695</t>
+          <t>637156</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>665818</t>
+          <t>666021</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1256728</t>
+          <t>1258420</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1299398</t>
+          <t>1299717</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>11636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14652</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22937</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44376</t>
+          <t>44493</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52609</t>
+          <t>52770</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49810</t>
+          <t>50205</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59309</t>
+          <t>59619</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97654</t>
+          <t>98039</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110301</t>
+          <t>110269</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>12266</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95739</t>
+          <t>95689</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101822</t>
+          <t>101829</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101160</t>
+          <t>101018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107381</t>
+          <t>107392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>199637</t>
+          <t>199454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>208062</t>
+          <t>207928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12947</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57304</t>
+          <t>57596</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64755</t>
+          <t>65166</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63673</t>
+          <t>63626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69250</t>
+          <t>69235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123789</t>
+          <t>123180</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133225</t>
+          <t>133110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27029</t>
+          <t>26794</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62134</t>
+          <t>62299</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71938</t>
+          <t>71768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65936</t>
+          <t>64879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75804</t>
+          <t>76022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131116</t>
+          <t>131351</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>145604</t>
+          <t>145606</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40378</t>
+          <t>40225</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42421</t>
+          <t>41788</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84665</t>
+          <t>84655</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>89190</t>
+          <t>89191</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,47 +9109,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22,66%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>7957</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>4161</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>13526</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>13,97%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>7,31%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>21,86%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>7957</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>4068</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>12950</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>13,97%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22318</t>
+          <t>21740</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42409</t>
+          <t>41974</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50306</t>
+          <t>50316</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,49 +9222,49 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>92,71%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>48991</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>43422</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>52787</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>86,03%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>76,25%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>92,69%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>48991</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>43998</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>52880</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>86,03%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>77,26%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>92,86%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>133</t>
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>88903</t>
+          <t>89481</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101230</t>
+          <t>101440</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>12595</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15137</t>
+          <t>14700</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10399</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23109</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124782</t>
+          <t>124779</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>133403</t>
+          <t>133481</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128263</t>
+          <t>128700</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>138146</t>
+          <t>138250</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>257665</t>
+          <t>257730</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>270294</t>
+          <t>270375</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>10964</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22833</t>
+          <t>22987</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>150778</t>
+          <t>150935</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>159635</t>
+          <t>159761</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>157078</t>
+          <t>157056</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>166325</t>
+          <t>166220</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>312192</t>
+          <t>312038</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>324048</t>
+          <t>324061</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37149</t>
+          <t>37234</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58633</t>
+          <t>59554</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41248</t>
+          <t>40454</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63708</t>
+          <t>62554</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>82772</t>
+          <t>83244</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>114153</t>
+          <t>115865</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>643595</t>
+          <t>642674</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>665079</t>
+          <t>664994</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>678064</t>
+          <t>679218</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>700524</t>
+          <t>701318</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1329847</t>
+          <t>1328135</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1361228</t>
+          <t>1360756</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30733</t>
+          <t>29365</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>21622</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17726</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45173</t>
+          <t>44760</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42549</t>
+          <t>43917</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67011</t>
+          <t>67151</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58227</t>
+          <t>57744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71116</t>
+          <t>71204</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107475</t>
+          <t>107888</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134922</t>
+          <t>135003</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>13959</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9920</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24657</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113150</t>
+          <t>112880</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123830</t>
+          <t>123754</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112211</t>
+          <t>112615</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>122820</t>
+          <t>122850</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>229778</t>
+          <t>230098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>244765</t>
+          <t>244515</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23308</t>
+          <t>22941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45589</t>
+          <t>46443</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54170</t>
+          <t>54406</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53399</t>
+          <t>52911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62663</t>
+          <t>62428</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>102123</t>
+          <t>102490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114622</t>
+          <t>114983</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16023</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43544</t>
+          <t>45246</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18634</t>
+          <t>18897</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>61563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,52%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54120</t>
+          <t>55171</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65228</t>
+          <t>65205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34590</t>
+          <t>32888</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67671</t>
+          <t>68112</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87398</t>
+          <t>86715</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129644</t>
+          <t>129381</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11771</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>27743</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33427</t>
+          <t>33147</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32579</t>
+          <t>32596</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>39108</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63461</t>
+          <t>63239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71238</t>
+          <t>70943</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>8165</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16734</t>
+          <t>16996</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21857</t>
+          <t>22345</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38002</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44403</t>
+          <t>44390</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39452</t>
+          <t>39190</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48814</t>
+          <t>48722</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80496</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>91502</t>
+          <t>91544</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16373</t>
+          <t>17089</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14815</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31879</t>
+          <t>32108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23361</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43473</t>
+          <t>43151</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108135</t>
+          <t>107419</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118300</t>
+          <t>118456</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>123324</t>
+          <t>123095</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>140388</t>
+          <t>140690</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>236239</t>
+          <t>236561</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>256351</t>
+          <t>257143</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14424</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13931</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10791</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>23836</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>116752</t>
+          <t>117952</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>126442</t>
+          <t>126576</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>141685</t>
+          <t>141688</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>151272</t>
+          <t>151696</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>262992</t>
+          <t>262956</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>276001</t>
+          <t>275817</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49681</t>
+          <t>49148</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>83860</t>
+          <t>82883</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>80646</t>
+          <t>80504</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>131983</t>
+          <t>133640</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>138048</t>
+          <t>137584</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>208543</t>
+          <t>200782</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>581036</t>
+          <t>582013</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>615215</t>
+          <t>615748</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>628001</t>
+          <t>626344</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>679338</t>
+          <t>679480</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1216338</t>
+          <t>1224099</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1286833</t>
+          <t>1287297</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,34%</t>
         </is>
       </c>
     </row>
